--- a/画面設計/【画面設計】01_メニュー画面.xlsx
+++ b/画面設計/【画面設計】01_メニュー画面.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="64">
   <si>
     <t>アプリ課題(2025）</t>
   </si>
@@ -69,15 +69,6 @@
   </si>
   <si>
     <t>【初期表示】（VB.NET)</t>
-  </si>
-  <si>
-    <t>【スマホ版イメージ】ハンバーガーメニューで作る。（アプリ起動時は料理検索がトップ）</t>
-  </si>
-  <si>
-    <t>←　ログイン状態かつログインユーザが権限ありの時だけ、レシピ登録のメニューを表示させる。</t>
-  </si>
-  <si>
-    <t>【スマホ版イメージ】ヘッダーメニューで作る。（全画面に読ませる）</t>
   </si>
   <si>
     <t>※ログアウトボタンはログイン時のみ表示</t>
@@ -158,7 +149,7 @@
 ログインユーザ情報のセッションを削除して、ゲスト扱いにする。</t>
   </si>
   <si>
-    <t>履歴マーク</t>
+    <t>時計マーク</t>
   </si>
   <si>
     <t>ユーザログイン中のみ表示。
@@ -741,12 +732,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>5467350</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4105275</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4800600" cy="2028825"/>
+    <xdr:ext cx="5810250" cy="7229475"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
         <xdr:cNvPr id="2" name="Shape 2" title="図形描画"/>
@@ -755,9 +746,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="152400" y="152400"/>
-          <a:ext cx="6248400" cy="2628900"/>
+          <a:ext cx="4171950" cy="5200650"/>
           <a:chOff x="152400" y="152400"/>
-          <a:chExt cx="6248400" cy="2628900"/>
+          <a:chExt cx="4171950" cy="5200650"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
@@ -776,58 +767,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="152400" y="152400"/>
-            <a:ext cx="6248400" cy="2628900"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1971675" cy="3971925"/>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="Shape 2" title="図形描画"/>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="152400" y="152400"/>
-          <a:ext cx="2674609" cy="5410202"/>
-          <a:chOff x="152400" y="152400"/>
-          <a:chExt cx="2674609" cy="5410202"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="5" name="Shape 5"/>
-          <xdr:cNvPicPr preferRelativeResize="0"/>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip r:embed="rId3">
-            <a:alphaModFix/>
-          </a:blip>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="152400" y="152400"/>
-            <a:ext cx="2674609" cy="5410202"/>
+            <a:ext cx="4171950" cy="5200650"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -855,7 +795,7 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -879,11 +819,11 @@
     <xdr:ext cx="228600" cy="228600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png"/>
+        <xdr:cNvPr id="0" name="image6.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -907,11 +847,11 @@
     <xdr:ext cx="219075" cy="228600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png"/>
+        <xdr:cNvPr id="0" name="image3.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -935,11 +875,11 @@
     <xdr:ext cx="638175" cy="228600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -963,11 +903,11 @@
     <xdr:ext cx="219075" cy="228600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
+        <xdr:cNvPr id="0" name="image4.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -991,11 +931,11 @@
     <xdr:ext cx="352425" cy="409575"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png"/>
+        <xdr:cNvPr id="0" name="image1.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2613,9 +2553,7 @@
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
-      <c r="E5" s="26" t="s">
-        <v>17</v>
-      </c>
+      <c r="E5" s="26"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="27"/>
@@ -2898,9 +2836,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="28" t="s">
-        <v>18</v>
-      </c>
+      <c r="H15" s="28"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="6"/>
@@ -3203,9 +3139,7 @@
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="26" t="s">
-        <v>19</v>
-      </c>
+      <c r="E26" s="26"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="27"/>
@@ -3542,7 +3476,7 @@
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -3572,7 +3506,7 @@
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="26" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
@@ -3599,7 +3533,7 @@
     <row r="40" ht="16.5" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
@@ -3629,7 +3563,7 @@
     <row r="41" ht="16.5" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -3738,7 +3672,7 @@
     <row r="45" ht="16.5" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -3768,13 +3702,13 @@
     <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="6"/>
       <c r="B46" s="32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -3858,7 +3792,7 @@
     <row r="49" ht="16.5" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -3888,7 +3822,7 @@
     <row r="50" ht="16.5" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -3918,10 +3852,10 @@
     <row r="51" ht="16.5" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D51" s="21"/>
       <c r="E51" s="6"/>
@@ -3950,10 +3884,10 @@
     <row r="52" ht="20.25" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="6"/>
@@ -3982,10 +3916,10 @@
     <row r="53" ht="20.25" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="40" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C53" s="41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="6"/>
@@ -4014,10 +3948,10 @@
     <row r="54" ht="36.75" customHeight="1">
       <c r="A54" s="6"/>
       <c r="B54" s="40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C54" s="41" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="6"/>
@@ -4046,10 +3980,10 @@
     <row r="55" ht="20.25" customHeight="1">
       <c r="A55" s="6"/>
       <c r="B55" s="42" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C55" s="41" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="6"/>
@@ -4106,7 +4040,7 @@
     <row r="57" ht="16.5" customHeight="1">
       <c r="A57" s="6"/>
       <c r="B57" s="36" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
@@ -4136,10 +4070,10 @@
     <row r="58" ht="16.5" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="6"/>
@@ -4168,10 +4102,10 @@
     <row r="59" ht="18.75" customHeight="1">
       <c r="A59" s="6"/>
       <c r="B59" s="43" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C59" s="41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="6"/>
@@ -4200,10 +4134,10 @@
     <row r="60" ht="41.25" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C60" s="44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="6"/>
@@ -4232,10 +4166,10 @@
     <row r="61" ht="34.5" customHeight="1">
       <c r="A61" s="6"/>
       <c r="B61" s="43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C61" s="41" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="6"/>
@@ -4264,10 +4198,10 @@
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="6"/>
       <c r="B62" s="43" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C62" s="44" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="6"/>
@@ -4324,14 +4258,14 @@
     <row r="64" ht="16.5" customHeight="1">
       <c r="A64" s="6"/>
       <c r="B64" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="26"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
@@ -4356,7 +4290,7 @@
     <row r="65" ht="16.5" customHeight="1">
       <c r="A65" s="6"/>
       <c r="B65" s="36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
@@ -4386,30 +4320,30 @@
     <row r="66" ht="16.5" customHeight="1">
       <c r="A66" s="6"/>
       <c r="B66" s="32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C66" s="32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H66" s="32" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I66" s="32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J66" s="32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K66" s="32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
@@ -4430,10 +4364,10 @@
     <row r="67" ht="18.0" customHeight="1">
       <c r="A67" s="45"/>
       <c r="B67" s="46" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D67" s="48"/>
       <c r="E67" s="25"/>
@@ -4463,10 +4397,10 @@
       <c r="A68" s="25"/>
       <c r="B68" s="40"/>
       <c r="C68" s="47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D68" s="50" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E68" s="25"/>
       <c r="F68" s="45"/>
@@ -4494,10 +4428,10 @@
     <row r="69" ht="18.0" customHeight="1">
       <c r="A69" s="45"/>
       <c r="B69" s="51" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D69" s="48"/>
       <c r="E69" s="25"/>
@@ -4527,10 +4461,10 @@
       <c r="A70" s="25"/>
       <c r="B70" s="40"/>
       <c r="C70" s="47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D70" s="52" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E70" s="25"/>
       <c r="F70" s="45"/>
@@ -4558,13 +4492,13 @@
     <row r="71" ht="36.0" customHeight="1">
       <c r="A71" s="45"/>
       <c r="B71" s="40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D71" s="52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E71" s="25"/>
       <c r="F71" s="45"/>
@@ -4592,10 +4526,10 @@
     <row r="72" ht="18.0" customHeight="1">
       <c r="A72" s="45"/>
       <c r="B72" s="53" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C72" s="47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D72" s="48"/>
       <c r="E72" s="25"/>
@@ -4625,10 +4559,10 @@
       <c r="A73" s="25"/>
       <c r="B73" s="40"/>
       <c r="C73" s="47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D73" s="52" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E73" s="25"/>
       <c r="F73" s="45"/>
@@ -4684,7 +4618,7 @@
     <row r="75" ht="16.5" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="36" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
@@ -4714,30 +4648,30 @@
     <row r="76" ht="16.5" customHeight="1">
       <c r="A76" s="6"/>
       <c r="B76" s="32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H76" s="32" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I76" s="32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J76" s="32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K76" s="32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
@@ -4759,10 +4693,10 @@
       <c r="A77" s="45"/>
       <c r="B77" s="46"/>
       <c r="C77" s="47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D77" s="47" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E77" s="25"/>
       <c r="F77" s="45"/>
@@ -4791,10 +4725,10 @@
       <c r="A78" s="45"/>
       <c r="B78" s="54"/>
       <c r="C78" s="47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E78" s="25"/>
       <c r="F78" s="45"/>
@@ -4822,13 +4756,13 @@
     <row r="79" ht="49.5" customHeight="1">
       <c r="A79" s="45"/>
       <c r="B79" s="43" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C79" s="47" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D79" s="55" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E79" s="25"/>
       <c r="F79" s="45"/>
@@ -4856,13 +4790,13 @@
     <row r="80" ht="33.0" customHeight="1">
       <c r="A80" s="45"/>
       <c r="B80" s="43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E80" s="25"/>
       <c r="F80" s="45"/>
@@ -4891,10 +4825,10 @@
       <c r="A81" s="45"/>
       <c r="B81" s="57"/>
       <c r="C81" s="47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D81" s="47" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E81" s="25"/>
       <c r="F81" s="45"/>
@@ -4923,10 +4857,10 @@
       <c r="A82" s="45"/>
       <c r="B82" s="54"/>
       <c r="C82" s="47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E82" s="25"/>
       <c r="F82" s="45"/>
@@ -4955,10 +4889,10 @@
       <c r="A83" s="45"/>
       <c r="B83" s="43"/>
       <c r="C83" s="43" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D83" s="55" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E83" s="25"/>
       <c r="F83" s="45"/>
@@ -30397,7 +30331,7 @@
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59"/>
       <c r="B4" s="59" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
@@ -30425,10 +30359,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" s="61" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="59"/>
